--- a/data/trans_orig/IP07A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A03-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82499</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72015</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90971</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>70056</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60782</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>78834</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>60587</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>79738</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,93%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>82499</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73004</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>91948</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,86%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139223</t>
+          <t>139015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164444</t>
+          <t>164778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50151</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41654</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59334</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51029</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42176</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59976</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42088</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60238</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50151</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40858</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>59262</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>89096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114276</t>
+          <t>114673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6477</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11326</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5089</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9629</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9476</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,99%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6477</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3238</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1066,67 +1066,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4558</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140163</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140163</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>105475</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93263</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>116770</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>103468</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>91833</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113867</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>92388</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>114986</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>105475</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93684</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>116405</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192419</t>
+          <t>190667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224271</t>
+          <t>223692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83643</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73384</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95294</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>71998</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61772</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83934</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>61625</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>83024</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83643</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73606</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95255</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139428</t>
+          <t>141372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171114</t>
+          <t>171985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7909</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18958</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18631</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12477</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13241</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26153</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,6%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8050</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19103</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4842</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1856,92 +1856,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3797</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202726</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202726</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202726</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202726</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202726</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202726</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>187975</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>172822</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>202861</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>50,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>173524</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>158335</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>187878</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>161278</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>187795</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>187975</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>173317</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>203284</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340408</t>
+          <t>340233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>383221</t>
+          <t>382195</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133794</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>117965</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>148718</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123027</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109105</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>137413</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>109082</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>136190</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>133794</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>118573</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148254</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236714</t>
+          <t>237426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278026</t>
+          <t>276403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13055</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26532</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>23720</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17318</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32985</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17117</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>31925</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,37%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>18739</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>12865</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>26881</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54172</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5203</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2538,92 +2538,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2691</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>342890</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>342890</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>342890</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321645</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>342890</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>342890</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81820</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70729</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>91428</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>89055</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>78820</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>98882</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>78786</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>99424</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81820</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>72208</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>91930</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187314</t>
+          <t>185121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67213</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57696</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78564</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56140</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46755</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67278</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45484</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66063</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67213</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57856</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77530</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109297</t>
+          <t>109446</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137674</t>
+          <t>137446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5163</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8723</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4692</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14361</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5163</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9684</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>3,3%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5436</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4945</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3455,102 +3455,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>680</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3113</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4574</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>94865</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84150</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106038</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>79552</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>69008</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89537</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>69570</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90231</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>94865</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84508</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>105434</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158621</t>
+          <t>158558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189670</t>
+          <t>187525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63616</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53637</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74030</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68753</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57852</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>79074</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58526</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78948</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63616</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54362</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74219</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117635</t>
+          <t>119425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146561</t>
+          <t>148590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14539</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9246</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21829</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15700</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22348</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10191</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22291</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14539</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9432</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21369</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>40279</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5818</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5193</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5027</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4137,102 +4137,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3468</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>798</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4231</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3505</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4626</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>176684</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>160931</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>190905</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>168607</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>152848</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>182134</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>153999</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>183038</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>176684</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>162372</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>191380</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>325855</t>
+          <t>324841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366879</t>
+          <t>365530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>130830</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>117109</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144742</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>124893</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>111662</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>140446</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>109965</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>139273</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>130830</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>116034</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>144522</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235986</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276470</t>
+          <t>275556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19702</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13439</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27955</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>24422</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17827</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32521</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>16882</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>32118</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,6%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>19702</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13530</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>27918</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54790</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1974</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6159</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7029</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3986</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8531</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4819,67 +4819,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1478</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321375</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321375</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321375</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber estado contento/a con su forma de ser, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>119217</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>108896</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>129605</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>69,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>114537</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>102783</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>125654</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>103651</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>125079</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>119217</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>108091</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>128824</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>63,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218418</t>
+          <t>218544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249406</t>
+          <t>248330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59046</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49526</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68975</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>62436</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52024</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73421</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52484</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73528</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59046</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49202</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69581</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107465</t>
+          <t>106625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137170</t>
+          <t>136789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7620</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4045</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12838</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5653</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11263</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2391</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11367</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7620</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13065</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3356</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7693</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8258</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>186643</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>186643</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>186643</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>186643</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>186643</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>186643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108954</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>96611</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>118424</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>93754</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82970</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105987</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>84473</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>104524</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>108954</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98260</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>119035</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186506</t>
+          <t>188727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217987</t>
+          <t>218976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46677</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67554</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>63757</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53266</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74795</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53632</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73858</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55844</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>46148</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66772</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106182</t>
+          <t>103559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135645</t>
+          <t>133938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8359</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14318</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11081</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6428</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17568</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17674</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8359</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4662</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13962</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5029</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1673</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5510</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6216</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4690</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -6408,107 +6408,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2962</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>228170</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>212505</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>242754</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>208291</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>192215</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>223049</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>193306</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>224777</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>228170</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>212706</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>243769</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410405</t>
+          <t>412950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>456424</t>
+          <t>456906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114890</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130886</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>126194</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>110795</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>140169</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112068</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>140724</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>114890</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>99998</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>130097</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220882</t>
+          <t>221615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266351</t>
+          <t>263587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -6869,67 +6869,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>15979</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10154</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23041</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>16734</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11039</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24910</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10759</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>24571</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>15979</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>10670</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>22850</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5739</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>5029</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10489</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6714</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7090,107 +7090,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3119</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>360690</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>360690</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>360690</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>360690</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>360690</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>360690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
